--- a/sources/table_normalization/xlsx/economy-table73.xlsx
+++ b/sources/table_normalization/xlsx/economy-table73.xlsx
@@ -136,8 +136,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="d/mm/yy;@"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="d/mm/yy;@"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -222,7 +222,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,17 +254,23 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray0625">
-        <fgColor indexed="31"/>
-        <bgColor rgb="FF00B0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="gray0625">
+        <fgColor indexed="31"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="27">
     <border>
@@ -656,7 +662,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -664,13 +670,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -693,26 +699,26 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -724,42 +730,94 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -768,9 +826,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -780,78 +835,29 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="7" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1342,66 +1348,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="32.5">
-      <c r="A1" s="38"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="24" t="s">
+      <c r="A1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="31" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="35" t="s">
+      <c r="J1" s="48"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="37"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="52"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="40"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="28"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="57" t="s">
+      <c r="F3" s="35" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="8" t="s">
@@ -1426,17 +1432,17 @@
         <v>14</v>
       </c>
       <c r="N3" s="19"/>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="27" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="58"/>
+      <c r="A4" s="38"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="10" t="s">
         <v>17</v>
       </c>
@@ -1459,7 +1465,7 @@
         <v>17</v>
       </c>
       <c r="N4" s="20"/>
-      <c r="O4" s="60" t="s">
+      <c r="O4" s="34" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1790,37 +1796,37 @@
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="59">
         <v>405</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="29">
         <v>20</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="30">
         <v>40</v>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="31">
         <v>60</v>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="31">
         <v>20</v>
       </c>
-      <c r="K15" s="45">
+      <c r="K15" s="31">
         <v>90</v>
       </c>
-      <c r="L15" s="45">
+      <c r="L15" s="31">
         <v>60</v>
       </c>
-      <c r="M15" s="45">
+      <c r="M15" s="31">
         <v>80</v>
       </c>
-      <c r="N15" s="46">
+      <c r="N15" s="32">
         <v>20</v>
       </c>
-      <c r="O15" s="42">
+      <c r="O15" s="59">
         <v>15</v>
       </c>
     </row>
@@ -1843,17 +1849,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:N2"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:N2"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Tax Codes" prompt="The relevant Tax Code must be entered for each Cash Receipt Category." sqref="G3 H3 I3 J3 K3 L3 M3 N3"/>
